--- a/Feuilles/Je t'aime.xlsx
+++ b/Feuilles/Je t'aime.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanaismusic/Documents/CLIC/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanaismusic/Documents/CLIC/Feuilles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F44CF76C-D42B-DE49-9451-E3B497FBAF58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EA9FBD8-23B8-944D-9A50-9053139B1153}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="2040" windowWidth="28040" windowHeight="17440" xr2:uid="{2F1647A4-8C84-E14B-83BA-CB692A19D8A6}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
   <si>
     <t>MES</t>
   </si>
@@ -84,6 +84,9 @@
   </si>
   <si>
     <t>REFRAIN 5</t>
+  </si>
+  <si>
+    <t>LOOP</t>
   </si>
 </sst>
 </file>
@@ -463,10 +466,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85B34C31-2D9C-7940-9F39-E67ACD52E89F}">
-  <dimension ref="A1:D224"/>
+  <dimension ref="A1:E224"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -479,8 +482,11 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -494,7 +500,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -505,7 +511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -516,7 +522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -527,7 +533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -538,7 +544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -549,7 +555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -560,7 +566,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -571,7 +577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -582,7 +588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -593,7 +599,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -604,7 +610,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
@@ -618,7 +624,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
@@ -629,7 +635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
@@ -640,7 +646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>

--- a/Feuilles/Je t'aime.xlsx
+++ b/Feuilles/Je t'aime.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanaismusic/Documents/CLIC/Feuilles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EA9FBD8-23B8-944D-9A50-9053139B1153}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58C5E073-BD5A-364E-A496-5F3FB9F126B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="2040" windowWidth="28040" windowHeight="17440" xr2:uid="{2F1647A4-8C84-E14B-83BA-CB692A19D8A6}"/>
   </bookViews>
@@ -839,7 +839,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>32</v>
       </c>
@@ -850,7 +850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>33</v>
       </c>
@@ -861,7 +861,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>34</v>
       </c>
@@ -872,7 +872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>35</v>
       </c>
@@ -883,7 +883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>36</v>
       </c>
@@ -894,7 +894,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>37</v>
       </c>
@@ -907,8 +907,11 @@
       <c r="D38" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>38</v>
       </c>
@@ -919,7 +922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>39</v>
       </c>
@@ -930,7 +933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>40</v>
       </c>
@@ -941,7 +944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>41</v>
       </c>
@@ -952,7 +955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>42</v>
       </c>
@@ -963,7 +966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>43</v>
       </c>
@@ -974,7 +977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>44</v>
       </c>
@@ -985,7 +988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>45</v>
       </c>
@@ -998,8 +1001,11 @@
       <c r="D46" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>46</v>
       </c>
@@ -1010,7 +1016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>47</v>
       </c>
@@ -1021,7 +1027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>48</v>
       </c>
@@ -1032,7 +1038,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>49</v>
       </c>
@@ -1043,7 +1049,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>50</v>
       </c>
@@ -1054,7 +1060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>51</v>
       </c>
@@ -1065,7 +1071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>52</v>
       </c>
@@ -1076,7 +1082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>53</v>
       </c>
@@ -1089,8 +1095,11 @@
       <c r="D54" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>54</v>
       </c>
@@ -1101,7 +1110,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>55</v>
       </c>
@@ -1112,7 +1121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>56</v>
       </c>
@@ -1123,7 +1132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>57</v>
       </c>
@@ -1134,7 +1143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>58</v>
       </c>
@@ -1145,7 +1154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>59</v>
       </c>
@@ -1156,7 +1165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>60</v>
       </c>
@@ -1167,7 +1176,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>61</v>
       </c>
@@ -1178,7 +1187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>62</v>
       </c>
@@ -1189,7 +1198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>63</v>
       </c>
@@ -1200,7 +1209,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>64</v>
       </c>
@@ -1213,8 +1222,11 @@
       <c r="D65" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>65</v>
       </c>
@@ -1225,7 +1237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>66</v>
       </c>
@@ -1236,7 +1248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>67</v>
       </c>
@@ -1247,7 +1259,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>68</v>
       </c>
@@ -1258,7 +1270,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>69</v>
       </c>
@@ -1269,7 +1281,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>70</v>
       </c>
@@ -1280,7 +1292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>71</v>
       </c>
@@ -1291,7 +1303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>72</v>
       </c>
@@ -1304,8 +1316,11 @@
       <c r="D73" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>73</v>
       </c>
@@ -1316,7 +1331,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>74</v>
       </c>
@@ -1327,7 +1342,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>75</v>
       </c>
@@ -1338,7 +1353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>76</v>
       </c>
@@ -1349,7 +1364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>77</v>
       </c>
@@ -1360,7 +1375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>78</v>
       </c>
@@ -1373,8 +1388,11 @@
       <c r="D79" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E79">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>79</v>
       </c>
@@ -1385,7 +1403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>80</v>
       </c>
@@ -1396,7 +1414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>81</v>
       </c>
@@ -1407,7 +1425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>82</v>
       </c>
@@ -1418,7 +1436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>83</v>
       </c>
@@ -1429,7 +1447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>84</v>
       </c>
@@ -1440,7 +1458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>85</v>
       </c>
@@ -1451,7 +1469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>86</v>
       </c>
@@ -1464,8 +1482,11 @@
       <c r="D87" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>87</v>
       </c>
@@ -1476,7 +1497,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>88</v>
       </c>
@@ -1490,7 +1511,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>89</v>
       </c>
@@ -1501,7 +1522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>90</v>
       </c>
@@ -1512,7 +1533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>91</v>
       </c>
@@ -1523,7 +1544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>92</v>
       </c>
@@ -1534,7 +1555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>93</v>
       </c>
@@ -1545,7 +1566,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>94</v>
       </c>
@@ -1556,7 +1577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A96">
         <v>95</v>
       </c>
